--- a/Lab4/recuento_manual_clusters.xlsx
+++ b/Lab4/recuento_manual_clusters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6798534934a44121/Documentos/Repositorio AstroML/AstroML_202610/Lab4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="11_AD4D2F04E46CFB4ACB3E20AD8554DF50683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845A180A-BE92-43DE-AC69-6357F586E62A}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="11_AD4D2F04E46CFB4ACB3E20AD8554DF50683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976E8A5B-28DC-48AC-BB69-42AD33B6DD47}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="63">
   <si>
     <t>38_000</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>Mejor clasif a 130</t>
+  </si>
+  <si>
+    <t>38_001 en 130 pc</t>
   </si>
 </sst>
 </file>
@@ -268,10 +271,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +569,7 @@
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -581,7 +583,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -594,8 +596,11 @@
       <c r="D2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -609,7 +614,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -623,7 +628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -634,7 +639,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -644,11 +649,11 @@
       <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -658,11 +663,11 @@
       <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -676,7 +681,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -690,7 +695,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -698,7 +703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -712,7 +717,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -726,7 +731,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -737,7 +742,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -751,7 +756,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -765,7 +770,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>

--- a/Lab4/recuento_manual_clusters.xlsx
+++ b/Lab4/recuento_manual_clusters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6798534934a44121/Documentos/Repositorio AstroML/AstroML_202610/Lab4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\japar\OneDrive\Documentos\Repositorio AstroML\AstroML_202610\Lab4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="11_AD4D2F04E46CFB4ACB3E20AD8554DF50683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{976E8A5B-28DC-48AC-BB69-42AD33B6DD47}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C09F90A-7280-42B1-B1DD-72B229453472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -251,12 +251,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -271,9 +277,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -289,10 +296,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,17 +562,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
@@ -583,7 +586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -600,7 +603,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -614,7 +617,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -628,7 +631,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -639,35 +642,35 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -677,11 +680,11 @@
       <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -691,11 +694,11 @@
       <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -703,7 +706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -713,11 +716,11 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -727,22 +730,22 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -752,11 +755,11 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -766,22 +769,22 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -791,12 +794,12 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="2" t="s">
         <v>52</v>
       </c>
       <c r="O17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -806,12 +809,12 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -821,11 +824,11 @@
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -835,11 +838,11 @@
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -849,11 +852,11 @@
       <c r="C21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -863,11 +866,11 @@
       <c r="C22" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -877,11 +880,11 @@
       <c r="C23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -892,7 +895,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -903,7 +906,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -911,7 +914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -919,43 +922,43 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C28" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C30" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -963,7 +966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -971,18 +974,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C33" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -990,18 +993,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C35" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1028,40 +1031,40 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C39" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C40" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
-      <c r="C41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1071,11 +1074,11 @@
       <c r="C42" t="s">
         <v>10</v>
       </c>
-      <c r="D42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
